--- a/astro-site/public/dl/kit-gestion-personal/01-cuadrante-turnos-semanal.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/01-cuadrante-turnos-semanal.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cuadrante Semanal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cuadrante Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadrante Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadrante Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cuadrante Semanal'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -168,57 +170,57 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="6" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -578,15 +580,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -594,6 +597,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -629,9 +633,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -660,9 +662,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -705,8 +705,25 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -715,21 +732,21 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="16"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -773,6 +790,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -836,7 +854,7 @@
       <c r="H6" s="13" t="n"/>
       <c r="I6" s="14">
         <f>IF(B6="M",8,IF(B6="T",8,IF(B6="N",8,IF(B6="P",9,0))))+IF(C6="M",8,IF(C6="T",8,IF(C6="N",8,IF(C6="P",9,0))))+IF(D6="M",8,IF(D6="T",8,IF(D6="N",8,IF(D6="P",9,0))))+IF(E6="M",8,IF(E6="T",8,IF(E6="N",8,IF(E6="P",9,0))))+IF(F6="M",8,IF(F6="T",8,IF(F6="N",8,IF(F6="P",9,0))))+IF(G6="M",8,IF(G6="T",8,IF(G6="N",8,IF(G6="P",9,0))))+IF(H6="M",8,IF(H6="T",8,IF(H6="N",8,IF(H6="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J6" s="15">
         <f>IF(I6&gt;40,"⚠ EXCESO",IF(I6&gt;0,"OK",""))</f>
@@ -854,7 +872,7 @@
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="14">
         <f>IF(B7="M",8,IF(B7="T",8,IF(B7="N",8,IF(B7="P",9,0))))+IF(C7="M",8,IF(C7="T",8,IF(C7="N",8,IF(C7="P",9,0))))+IF(D7="M",8,IF(D7="T",8,IF(D7="N",8,IF(D7="P",9,0))))+IF(E7="M",8,IF(E7="T",8,IF(E7="N",8,IF(E7="P",9,0))))+IF(F7="M",8,IF(F7="T",8,IF(F7="N",8,IF(F7="P",9,0))))+IF(G7="M",8,IF(G7="T",8,IF(G7="N",8,IF(G7="P",9,0))))+IF(H7="M",8,IF(H7="T",8,IF(H7="N",8,IF(H7="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J7" s="15">
         <f>IF(I7&gt;40,"⚠ EXCESO",IF(I7&gt;0,"OK",""))</f>
@@ -872,7 +890,7 @@
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="14">
         <f>IF(B8="M",8,IF(B8="T",8,IF(B8="N",8,IF(B8="P",9,0))))+IF(C8="M",8,IF(C8="T",8,IF(C8="N",8,IF(C8="P",9,0))))+IF(D8="M",8,IF(D8="T",8,IF(D8="N",8,IF(D8="P",9,0))))+IF(E8="M",8,IF(E8="T",8,IF(E8="N",8,IF(E8="P",9,0))))+IF(F8="M",8,IF(F8="T",8,IF(F8="N",8,IF(F8="P",9,0))))+IF(G8="M",8,IF(G8="T",8,IF(G8="N",8,IF(G8="P",9,0))))+IF(H8="M",8,IF(H8="T",8,IF(H8="N",8,IF(H8="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J8" s="15">
         <f>IF(I8&gt;40,"⚠ EXCESO",IF(I8&gt;0,"OK",""))</f>
@@ -890,7 +908,7 @@
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="14">
         <f>IF(B9="M",8,IF(B9="T",8,IF(B9="N",8,IF(B9="P",9,0))))+IF(C9="M",8,IF(C9="T",8,IF(C9="N",8,IF(C9="P",9,0))))+IF(D9="M",8,IF(D9="T",8,IF(D9="N",8,IF(D9="P",9,0))))+IF(E9="M",8,IF(E9="T",8,IF(E9="N",8,IF(E9="P",9,0))))+IF(F9="M",8,IF(F9="T",8,IF(F9="N",8,IF(F9="P",9,0))))+IF(G9="M",8,IF(G9="T",8,IF(G9="N",8,IF(G9="P",9,0))))+IF(H9="M",8,IF(H9="T",8,IF(H9="N",8,IF(H9="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J9" s="15">
         <f>IF(I9&gt;40,"⚠ EXCESO",IF(I9&gt;0,"OK",""))</f>
@@ -908,7 +926,7 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="14">
         <f>IF(B10="M",8,IF(B10="T",8,IF(B10="N",8,IF(B10="P",9,0))))+IF(C10="M",8,IF(C10="T",8,IF(C10="N",8,IF(C10="P",9,0))))+IF(D10="M",8,IF(D10="T",8,IF(D10="N",8,IF(D10="P",9,0))))+IF(E10="M",8,IF(E10="T",8,IF(E10="N",8,IF(E10="P",9,0))))+IF(F10="M",8,IF(F10="T",8,IF(F10="N",8,IF(F10="P",9,0))))+IF(G10="M",8,IF(G10="T",8,IF(G10="N",8,IF(G10="P",9,0))))+IF(H10="M",8,IF(H10="T",8,IF(H10="N",8,IF(H10="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J10" s="15">
         <f>IF(I10&gt;40,"⚠ EXCESO",IF(I10&gt;0,"OK",""))</f>
@@ -926,7 +944,7 @@
       <c r="H11" s="13" t="n"/>
       <c r="I11" s="14">
         <f>IF(B11="M",8,IF(B11="T",8,IF(B11="N",8,IF(B11="P",9,0))))+IF(C11="M",8,IF(C11="T",8,IF(C11="N",8,IF(C11="P",9,0))))+IF(D11="M",8,IF(D11="T",8,IF(D11="N",8,IF(D11="P",9,0))))+IF(E11="M",8,IF(E11="T",8,IF(E11="N",8,IF(E11="P",9,0))))+IF(F11="M",8,IF(F11="T",8,IF(F11="N",8,IF(F11="P",9,0))))+IF(G11="M",8,IF(G11="T",8,IF(G11="N",8,IF(G11="P",9,0))))+IF(H11="M",8,IF(H11="T",8,IF(H11="N",8,IF(H11="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J11" s="15">
         <f>IF(I11&gt;40,"⚠ EXCESO",IF(I11&gt;0,"OK",""))</f>
@@ -944,7 +962,7 @@
       <c r="H12" s="13" t="n"/>
       <c r="I12" s="14">
         <f>IF(B12="M",8,IF(B12="T",8,IF(B12="N",8,IF(B12="P",9,0))))+IF(C12="M",8,IF(C12="T",8,IF(C12="N",8,IF(C12="P",9,0))))+IF(D12="M",8,IF(D12="T",8,IF(D12="N",8,IF(D12="P",9,0))))+IF(E12="M",8,IF(E12="T",8,IF(E12="N",8,IF(E12="P",9,0))))+IF(F12="M",8,IF(F12="T",8,IF(F12="N",8,IF(F12="P",9,0))))+IF(G12="M",8,IF(G12="T",8,IF(G12="N",8,IF(G12="P",9,0))))+IF(H12="M",8,IF(H12="T",8,IF(H12="N",8,IF(H12="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J12" s="15">
         <f>IF(I12&gt;40,"⚠ EXCESO",IF(I12&gt;0,"OK",""))</f>
@@ -962,7 +980,7 @@
       <c r="H13" s="13" t="n"/>
       <c r="I13" s="14">
         <f>IF(B13="M",8,IF(B13="T",8,IF(B13="N",8,IF(B13="P",9,0))))+IF(C13="M",8,IF(C13="T",8,IF(C13="N",8,IF(C13="P",9,0))))+IF(D13="M",8,IF(D13="T",8,IF(D13="N",8,IF(D13="P",9,0))))+IF(E13="M",8,IF(E13="T",8,IF(E13="N",8,IF(E13="P",9,0))))+IF(F13="M",8,IF(F13="T",8,IF(F13="N",8,IF(F13="P",9,0))))+IF(G13="M",8,IF(G13="T",8,IF(G13="N",8,IF(G13="P",9,0))))+IF(H13="M",8,IF(H13="T",8,IF(H13="N",8,IF(H13="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J13" s="15">
         <f>IF(I13&gt;40,"⚠ EXCESO",IF(I13&gt;0,"OK",""))</f>
@@ -980,7 +998,7 @@
       <c r="H14" s="13" t="n"/>
       <c r="I14" s="14">
         <f>IF(B14="M",8,IF(B14="T",8,IF(B14="N",8,IF(B14="P",9,0))))+IF(C14="M",8,IF(C14="T",8,IF(C14="N",8,IF(C14="P",9,0))))+IF(D14="M",8,IF(D14="T",8,IF(D14="N",8,IF(D14="P",9,0))))+IF(E14="M",8,IF(E14="T",8,IF(E14="N",8,IF(E14="P",9,0))))+IF(F14="M",8,IF(F14="T",8,IF(F14="N",8,IF(F14="P",9,0))))+IF(G14="M",8,IF(G14="T",8,IF(G14="N",8,IF(G14="P",9,0))))+IF(H14="M",8,IF(H14="T",8,IF(H14="N",8,IF(H14="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J14" s="15">
         <f>IF(I14&gt;40,"⚠ EXCESO",IF(I14&gt;0,"OK",""))</f>
@@ -998,7 +1016,7 @@
       <c r="H15" s="13" t="n"/>
       <c r="I15" s="14">
         <f>IF(B15="M",8,IF(B15="T",8,IF(B15="N",8,IF(B15="P",9,0))))+IF(C15="M",8,IF(C15="T",8,IF(C15="N",8,IF(C15="P",9,0))))+IF(D15="M",8,IF(D15="T",8,IF(D15="N",8,IF(D15="P",9,0))))+IF(E15="M",8,IF(E15="T",8,IF(E15="N",8,IF(E15="P",9,0))))+IF(F15="M",8,IF(F15="T",8,IF(F15="N",8,IF(F15="P",9,0))))+IF(G15="M",8,IF(G15="T",8,IF(G15="N",8,IF(G15="P",9,0))))+IF(H15="M",8,IF(H15="T",8,IF(H15="N",8,IF(H15="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J15" s="15">
         <f>IF(I15&gt;40,"⚠ EXCESO",IF(I15&gt;0,"OK",""))</f>
@@ -1016,7 +1034,7 @@
       <c r="H16" s="13" t="n"/>
       <c r="I16" s="14">
         <f>IF(B16="M",8,IF(B16="T",8,IF(B16="N",8,IF(B16="P",9,0))))+IF(C16="M",8,IF(C16="T",8,IF(C16="N",8,IF(C16="P",9,0))))+IF(D16="M",8,IF(D16="T",8,IF(D16="N",8,IF(D16="P",9,0))))+IF(E16="M",8,IF(E16="T",8,IF(E16="N",8,IF(E16="P",9,0))))+IF(F16="M",8,IF(F16="T",8,IF(F16="N",8,IF(F16="P",9,0))))+IF(G16="M",8,IF(G16="T",8,IF(G16="N",8,IF(G16="P",9,0))))+IF(H16="M",8,IF(H16="T",8,IF(H16="N",8,IF(H16="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J16" s="15">
         <f>IF(I16&gt;40,"⚠ EXCESO",IF(I16&gt;0,"OK",""))</f>
@@ -1034,7 +1052,7 @@
       <c r="H17" s="13" t="n"/>
       <c r="I17" s="14">
         <f>IF(B17="M",8,IF(B17="T",8,IF(B17="N",8,IF(B17="P",9,0))))+IF(C17="M",8,IF(C17="T",8,IF(C17="N",8,IF(C17="P",9,0))))+IF(D17="M",8,IF(D17="T",8,IF(D17="N",8,IF(D17="P",9,0))))+IF(E17="M",8,IF(E17="T",8,IF(E17="N",8,IF(E17="P",9,0))))+IF(F17="M",8,IF(F17="T",8,IF(F17="N",8,IF(F17="P",9,0))))+IF(G17="M",8,IF(G17="T",8,IF(G17="N",8,IF(G17="P",9,0))))+IF(H17="M",8,IF(H17="T",8,IF(H17="N",8,IF(H17="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J17" s="15">
         <f>IF(I17&gt;40,"⚠ EXCESO",IF(I17&gt;0,"OK",""))</f>
@@ -1052,7 +1070,7 @@
       <c r="H18" s="13" t="n"/>
       <c r="I18" s="14">
         <f>IF(B18="M",8,IF(B18="T",8,IF(B18="N",8,IF(B18="P",9,0))))+IF(C18="M",8,IF(C18="T",8,IF(C18="N",8,IF(C18="P",9,0))))+IF(D18="M",8,IF(D18="T",8,IF(D18="N",8,IF(D18="P",9,0))))+IF(E18="M",8,IF(E18="T",8,IF(E18="N",8,IF(E18="P",9,0))))+IF(F18="M",8,IF(F18="T",8,IF(F18="N",8,IF(F18="P",9,0))))+IF(G18="M",8,IF(G18="T",8,IF(G18="N",8,IF(G18="P",9,0))))+IF(H18="M",8,IF(H18="T",8,IF(H18="N",8,IF(H18="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J18" s="15">
         <f>IF(I18&gt;40,"⚠ EXCESO",IF(I18&gt;0,"OK",""))</f>
@@ -1070,7 +1088,7 @@
       <c r="H19" s="13" t="n"/>
       <c r="I19" s="14">
         <f>IF(B19="M",8,IF(B19="T",8,IF(B19="N",8,IF(B19="P",9,0))))+IF(C19="M",8,IF(C19="T",8,IF(C19="N",8,IF(C19="P",9,0))))+IF(D19="M",8,IF(D19="T",8,IF(D19="N",8,IF(D19="P",9,0))))+IF(E19="M",8,IF(E19="T",8,IF(E19="N",8,IF(E19="P",9,0))))+IF(F19="M",8,IF(F19="T",8,IF(F19="N",8,IF(F19="P",9,0))))+IF(G19="M",8,IF(G19="T",8,IF(G19="N",8,IF(G19="P",9,0))))+IF(H19="M",8,IF(H19="T",8,IF(H19="N",8,IF(H19="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J19" s="15">
         <f>IF(I19&gt;40,"⚠ EXCESO",IF(I19&gt;0,"OK",""))</f>
@@ -1088,7 +1106,7 @@
       <c r="H20" s="13" t="n"/>
       <c r="I20" s="14">
         <f>IF(B20="M",8,IF(B20="T",8,IF(B20="N",8,IF(B20="P",9,0))))+IF(C20="M",8,IF(C20="T",8,IF(C20="N",8,IF(C20="P",9,0))))+IF(D20="M",8,IF(D20="T",8,IF(D20="N",8,IF(D20="P",9,0))))+IF(E20="M",8,IF(E20="T",8,IF(E20="N",8,IF(E20="P",9,0))))+IF(F20="M",8,IF(F20="T",8,IF(F20="N",8,IF(F20="P",9,0))))+IF(G20="M",8,IF(G20="T",8,IF(G20="N",8,IF(G20="P",9,0))))+IF(H20="M",8,IF(H20="T",8,IF(H20="N",8,IF(H20="P",9,0))))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J20" s="15">
         <f>IF(I20&gt;40,"⚠ EXCESO",IF(I20&gt;0,"OK",""))</f>
@@ -1103,9 +1121,10 @@
       </c>
       <c r="I21" s="14">
         <f>SUM(I6:I20)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
@@ -1120,11 +1139,20 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa M, T, N, P o L" prompt="M=Mañana, T=Tarde, N=Noche, P=Partido, L=Libre" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20" type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa M, T, N, P o L" prompt="M=Mañana, T=Tarde, N=Noche, P=Partido, L=Libre" type="list">
       <formula1>"M,T,N,P,L"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1133,20 +1161,20 @@
   <sheetPr>
     <tabColor rgb="000D47A1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="12"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="12"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
-    <col customWidth="1" max="8" min="8" width="12"/>
-    <col customWidth="1" max="9" min="9" width="12"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1382,6 +1410,8 @@
       <c r="H19" s="20" t="n"/>
       <c r="I19" s="20" t="n"/>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -1601,6 +1631,8 @@
       <c r="H38" s="20" t="n"/>
       <c r="I38" s="20" t="n"/>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
@@ -1820,6 +1852,8 @@
       <c r="H57" s="20" t="n"/>
       <c r="I57" s="20" t="n"/>
     </row>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
@@ -2039,6 +2073,9 @@
       <c r="H76" s="20" t="n"/>
       <c r="I76" s="20" t="n"/>
     </row>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
@@ -2052,6 +2089,15 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A80:I80"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/01-cuadrante-turnos-semanal.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/01-cuadrante-turnos-semanal.xlsx
@@ -1,19 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadrante Semanal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadrante Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cuadrante Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cuadrante Mensual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Cuadrante Semanal'!$5:$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -170,57 +168,57 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="6" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="8" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -580,16 +578,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="B2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -597,7 +594,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -633,7 +629,9 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="B9" t="inlineStr"/>
+    </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -662,7 +660,9 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="B14" t="inlineStr"/>
+    </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -705,25 +705,8 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -732,21 +715,21 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="14"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="14"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="14"/>
+    <col customWidth="1" max="10" min="10" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,7 +773,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -854,7 +836,7 @@
       <c r="H6" s="13" t="n"/>
       <c r="I6" s="14">
         <f>IF(B6="M",8,IF(B6="T",8,IF(B6="N",8,IF(B6="P",9,0))))+IF(C6="M",8,IF(C6="T",8,IF(C6="N",8,IF(C6="P",9,0))))+IF(D6="M",8,IF(D6="T",8,IF(D6="N",8,IF(D6="P",9,0))))+IF(E6="M",8,IF(E6="T",8,IF(E6="N",8,IF(E6="P",9,0))))+IF(F6="M",8,IF(F6="T",8,IF(F6="N",8,IF(F6="P",9,0))))+IF(G6="M",8,IF(G6="T",8,IF(G6="N",8,IF(G6="P",9,0))))+IF(H6="M",8,IF(H6="T",8,IF(H6="N",8,IF(H6="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J6" s="15">
         <f>IF(I6&gt;40,"⚠ EXCESO",IF(I6&gt;0,"OK",""))</f>
@@ -872,7 +854,7 @@
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="14">
         <f>IF(B7="M",8,IF(B7="T",8,IF(B7="N",8,IF(B7="P",9,0))))+IF(C7="M",8,IF(C7="T",8,IF(C7="N",8,IF(C7="P",9,0))))+IF(D7="M",8,IF(D7="T",8,IF(D7="N",8,IF(D7="P",9,0))))+IF(E7="M",8,IF(E7="T",8,IF(E7="N",8,IF(E7="P",9,0))))+IF(F7="M",8,IF(F7="T",8,IF(F7="N",8,IF(F7="P",9,0))))+IF(G7="M",8,IF(G7="T",8,IF(G7="N",8,IF(G7="P",9,0))))+IF(H7="M",8,IF(H7="T",8,IF(H7="N",8,IF(H7="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J7" s="15">
         <f>IF(I7&gt;40,"⚠ EXCESO",IF(I7&gt;0,"OK",""))</f>
@@ -890,7 +872,7 @@
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="14">
         <f>IF(B8="M",8,IF(B8="T",8,IF(B8="N",8,IF(B8="P",9,0))))+IF(C8="M",8,IF(C8="T",8,IF(C8="N",8,IF(C8="P",9,0))))+IF(D8="M",8,IF(D8="T",8,IF(D8="N",8,IF(D8="P",9,0))))+IF(E8="M",8,IF(E8="T",8,IF(E8="N",8,IF(E8="P",9,0))))+IF(F8="M",8,IF(F8="T",8,IF(F8="N",8,IF(F8="P",9,0))))+IF(G8="M",8,IF(G8="T",8,IF(G8="N",8,IF(G8="P",9,0))))+IF(H8="M",8,IF(H8="T",8,IF(H8="N",8,IF(H8="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J8" s="15">
         <f>IF(I8&gt;40,"⚠ EXCESO",IF(I8&gt;0,"OK",""))</f>
@@ -908,7 +890,7 @@
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="14">
         <f>IF(B9="M",8,IF(B9="T",8,IF(B9="N",8,IF(B9="P",9,0))))+IF(C9="M",8,IF(C9="T",8,IF(C9="N",8,IF(C9="P",9,0))))+IF(D9="M",8,IF(D9="T",8,IF(D9="N",8,IF(D9="P",9,0))))+IF(E9="M",8,IF(E9="T",8,IF(E9="N",8,IF(E9="P",9,0))))+IF(F9="M",8,IF(F9="T",8,IF(F9="N",8,IF(F9="P",9,0))))+IF(G9="M",8,IF(G9="T",8,IF(G9="N",8,IF(G9="P",9,0))))+IF(H9="M",8,IF(H9="T",8,IF(H9="N",8,IF(H9="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J9" s="15">
         <f>IF(I9&gt;40,"⚠ EXCESO",IF(I9&gt;0,"OK",""))</f>
@@ -926,7 +908,7 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="14">
         <f>IF(B10="M",8,IF(B10="T",8,IF(B10="N",8,IF(B10="P",9,0))))+IF(C10="M",8,IF(C10="T",8,IF(C10="N",8,IF(C10="P",9,0))))+IF(D10="M",8,IF(D10="T",8,IF(D10="N",8,IF(D10="P",9,0))))+IF(E10="M",8,IF(E10="T",8,IF(E10="N",8,IF(E10="P",9,0))))+IF(F10="M",8,IF(F10="T",8,IF(F10="N",8,IF(F10="P",9,0))))+IF(G10="M",8,IF(G10="T",8,IF(G10="N",8,IF(G10="P",9,0))))+IF(H10="M",8,IF(H10="T",8,IF(H10="N",8,IF(H10="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J10" s="15">
         <f>IF(I10&gt;40,"⚠ EXCESO",IF(I10&gt;0,"OK",""))</f>
@@ -944,7 +926,7 @@
       <c r="H11" s="13" t="n"/>
       <c r="I11" s="14">
         <f>IF(B11="M",8,IF(B11="T",8,IF(B11="N",8,IF(B11="P",9,0))))+IF(C11="M",8,IF(C11="T",8,IF(C11="N",8,IF(C11="P",9,0))))+IF(D11="M",8,IF(D11="T",8,IF(D11="N",8,IF(D11="P",9,0))))+IF(E11="M",8,IF(E11="T",8,IF(E11="N",8,IF(E11="P",9,0))))+IF(F11="M",8,IF(F11="T",8,IF(F11="N",8,IF(F11="P",9,0))))+IF(G11="M",8,IF(G11="T",8,IF(G11="N",8,IF(G11="P",9,0))))+IF(H11="M",8,IF(H11="T",8,IF(H11="N",8,IF(H11="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J11" s="15">
         <f>IF(I11&gt;40,"⚠ EXCESO",IF(I11&gt;0,"OK",""))</f>
@@ -962,7 +944,7 @@
       <c r="H12" s="13" t="n"/>
       <c r="I12" s="14">
         <f>IF(B12="M",8,IF(B12="T",8,IF(B12="N",8,IF(B12="P",9,0))))+IF(C12="M",8,IF(C12="T",8,IF(C12="N",8,IF(C12="P",9,0))))+IF(D12="M",8,IF(D12="T",8,IF(D12="N",8,IF(D12="P",9,0))))+IF(E12="M",8,IF(E12="T",8,IF(E12="N",8,IF(E12="P",9,0))))+IF(F12="M",8,IF(F12="T",8,IF(F12="N",8,IF(F12="P",9,0))))+IF(G12="M",8,IF(G12="T",8,IF(G12="N",8,IF(G12="P",9,0))))+IF(H12="M",8,IF(H12="T",8,IF(H12="N",8,IF(H12="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J12" s="15">
         <f>IF(I12&gt;40,"⚠ EXCESO",IF(I12&gt;0,"OK",""))</f>
@@ -980,7 +962,7 @@
       <c r="H13" s="13" t="n"/>
       <c r="I13" s="14">
         <f>IF(B13="M",8,IF(B13="T",8,IF(B13="N",8,IF(B13="P",9,0))))+IF(C13="M",8,IF(C13="T",8,IF(C13="N",8,IF(C13="P",9,0))))+IF(D13="M",8,IF(D13="T",8,IF(D13="N",8,IF(D13="P",9,0))))+IF(E13="M",8,IF(E13="T",8,IF(E13="N",8,IF(E13="P",9,0))))+IF(F13="M",8,IF(F13="T",8,IF(F13="N",8,IF(F13="P",9,0))))+IF(G13="M",8,IF(G13="T",8,IF(G13="N",8,IF(G13="P",9,0))))+IF(H13="M",8,IF(H13="T",8,IF(H13="N",8,IF(H13="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J13" s="15">
         <f>IF(I13&gt;40,"⚠ EXCESO",IF(I13&gt;0,"OK",""))</f>
@@ -998,7 +980,7 @@
       <c r="H14" s="13" t="n"/>
       <c r="I14" s="14">
         <f>IF(B14="M",8,IF(B14="T",8,IF(B14="N",8,IF(B14="P",9,0))))+IF(C14="M",8,IF(C14="T",8,IF(C14="N",8,IF(C14="P",9,0))))+IF(D14="M",8,IF(D14="T",8,IF(D14="N",8,IF(D14="P",9,0))))+IF(E14="M",8,IF(E14="T",8,IF(E14="N",8,IF(E14="P",9,0))))+IF(F14="M",8,IF(F14="T",8,IF(F14="N",8,IF(F14="P",9,0))))+IF(G14="M",8,IF(G14="T",8,IF(G14="N",8,IF(G14="P",9,0))))+IF(H14="M",8,IF(H14="T",8,IF(H14="N",8,IF(H14="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J14" s="15">
         <f>IF(I14&gt;40,"⚠ EXCESO",IF(I14&gt;0,"OK",""))</f>
@@ -1016,7 +998,7 @@
       <c r="H15" s="13" t="n"/>
       <c r="I15" s="14">
         <f>IF(B15="M",8,IF(B15="T",8,IF(B15="N",8,IF(B15="P",9,0))))+IF(C15="M",8,IF(C15="T",8,IF(C15="N",8,IF(C15="P",9,0))))+IF(D15="M",8,IF(D15="T",8,IF(D15="N",8,IF(D15="P",9,0))))+IF(E15="M",8,IF(E15="T",8,IF(E15="N",8,IF(E15="P",9,0))))+IF(F15="M",8,IF(F15="T",8,IF(F15="N",8,IF(F15="P",9,0))))+IF(G15="M",8,IF(G15="T",8,IF(G15="N",8,IF(G15="P",9,0))))+IF(H15="M",8,IF(H15="T",8,IF(H15="N",8,IF(H15="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J15" s="15">
         <f>IF(I15&gt;40,"⚠ EXCESO",IF(I15&gt;0,"OK",""))</f>
@@ -1034,7 +1016,7 @@
       <c r="H16" s="13" t="n"/>
       <c r="I16" s="14">
         <f>IF(B16="M",8,IF(B16="T",8,IF(B16="N",8,IF(B16="P",9,0))))+IF(C16="M",8,IF(C16="T",8,IF(C16="N",8,IF(C16="P",9,0))))+IF(D16="M",8,IF(D16="T",8,IF(D16="N",8,IF(D16="P",9,0))))+IF(E16="M",8,IF(E16="T",8,IF(E16="N",8,IF(E16="P",9,0))))+IF(F16="M",8,IF(F16="T",8,IF(F16="N",8,IF(F16="P",9,0))))+IF(G16="M",8,IF(G16="T",8,IF(G16="N",8,IF(G16="P",9,0))))+IF(H16="M",8,IF(H16="T",8,IF(H16="N",8,IF(H16="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J16" s="15">
         <f>IF(I16&gt;40,"⚠ EXCESO",IF(I16&gt;0,"OK",""))</f>
@@ -1052,7 +1034,7 @@
       <c r="H17" s="13" t="n"/>
       <c r="I17" s="14">
         <f>IF(B17="M",8,IF(B17="T",8,IF(B17="N",8,IF(B17="P",9,0))))+IF(C17="M",8,IF(C17="T",8,IF(C17="N",8,IF(C17="P",9,0))))+IF(D17="M",8,IF(D17="T",8,IF(D17="N",8,IF(D17="P",9,0))))+IF(E17="M",8,IF(E17="T",8,IF(E17="N",8,IF(E17="P",9,0))))+IF(F17="M",8,IF(F17="T",8,IF(F17="N",8,IF(F17="P",9,0))))+IF(G17="M",8,IF(G17="T",8,IF(G17="N",8,IF(G17="P",9,0))))+IF(H17="M",8,IF(H17="T",8,IF(H17="N",8,IF(H17="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J17" s="15">
         <f>IF(I17&gt;40,"⚠ EXCESO",IF(I17&gt;0,"OK",""))</f>
@@ -1070,7 +1052,7 @@
       <c r="H18" s="13" t="n"/>
       <c r="I18" s="14">
         <f>IF(B18="M",8,IF(B18="T",8,IF(B18="N",8,IF(B18="P",9,0))))+IF(C18="M",8,IF(C18="T",8,IF(C18="N",8,IF(C18="P",9,0))))+IF(D18="M",8,IF(D18="T",8,IF(D18="N",8,IF(D18="P",9,0))))+IF(E18="M",8,IF(E18="T",8,IF(E18="N",8,IF(E18="P",9,0))))+IF(F18="M",8,IF(F18="T",8,IF(F18="N",8,IF(F18="P",9,0))))+IF(G18="M",8,IF(G18="T",8,IF(G18="N",8,IF(G18="P",9,0))))+IF(H18="M",8,IF(H18="T",8,IF(H18="N",8,IF(H18="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J18" s="15">
         <f>IF(I18&gt;40,"⚠ EXCESO",IF(I18&gt;0,"OK",""))</f>
@@ -1088,7 +1070,7 @@
       <c r="H19" s="13" t="n"/>
       <c r="I19" s="14">
         <f>IF(B19="M",8,IF(B19="T",8,IF(B19="N",8,IF(B19="P",9,0))))+IF(C19="M",8,IF(C19="T",8,IF(C19="N",8,IF(C19="P",9,0))))+IF(D19="M",8,IF(D19="T",8,IF(D19="N",8,IF(D19="P",9,0))))+IF(E19="M",8,IF(E19="T",8,IF(E19="N",8,IF(E19="P",9,0))))+IF(F19="M",8,IF(F19="T",8,IF(F19="N",8,IF(F19="P",9,0))))+IF(G19="M",8,IF(G19="T",8,IF(G19="N",8,IF(G19="P",9,0))))+IF(H19="M",8,IF(H19="T",8,IF(H19="N",8,IF(H19="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J19" s="15">
         <f>IF(I19&gt;40,"⚠ EXCESO",IF(I19&gt;0,"OK",""))</f>
@@ -1106,7 +1088,7 @@
       <c r="H20" s="13" t="n"/>
       <c r="I20" s="14">
         <f>IF(B20="M",8,IF(B20="T",8,IF(B20="N",8,IF(B20="P",9,0))))+IF(C20="M",8,IF(C20="T",8,IF(C20="N",8,IF(C20="P",9,0))))+IF(D20="M",8,IF(D20="T",8,IF(D20="N",8,IF(D20="P",9,0))))+IF(E20="M",8,IF(E20="T",8,IF(E20="N",8,IF(E20="P",9,0))))+IF(F20="M",8,IF(F20="T",8,IF(F20="N",8,IF(F20="P",9,0))))+IF(G20="M",8,IF(G20="T",8,IF(G20="N",8,IF(G20="P",9,0))))+IF(H20="M",8,IF(H20="T",8,IF(H20="N",8,IF(H20="P",9,0))))</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="J20" s="15">
         <f>IF(I20&gt;40,"⚠ EXCESO",IF(I20&gt;0,"OK",""))</f>
@@ -1121,10 +1103,9 @@
       </c>
       <c r="I21" s="14">
         <f>SUM(I6:I20)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22"/>
+        <v/>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
@@ -1139,20 +1120,11 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa M, T, N, P o L" prompt="M=Mañana, T=Tarde, N=Noche, P=Partido, L=Libre" type="list">
+    <dataValidation allowBlank="1" error="Usa M, T, N, P o L" prompt="M=Mañana, T=Tarde, N=Noche, P=Partido, L=Libre" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20" type="list">
       <formula1>"M,T,N,P,L"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1161,20 +1133,20 @@
   <sheetPr>
     <tabColor rgb="000D47A1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="12"/>
+    <col customWidth="1" max="3" min="3" width="12"/>
+    <col customWidth="1" max="4" min="4" width="12"/>
+    <col customWidth="1" max="5" min="5" width="12"/>
+    <col customWidth="1" max="6" min="6" width="12"/>
+    <col customWidth="1" max="7" min="7" width="12"/>
+    <col customWidth="1" max="8" min="8" width="12"/>
+    <col customWidth="1" max="9" min="9" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1410,8 +1382,6 @@
       <c r="H19" s="20" t="n"/>
       <c r="I19" s="20" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -1631,8 +1601,6 @@
       <c r="H38" s="20" t="n"/>
       <c r="I38" s="20" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
@@ -1852,8 +1820,6 @@
       <c r="H57" s="20" t="n"/>
       <c r="I57" s="20" t="n"/>
     </row>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
@@ -2073,9 +2039,6 @@
       <c r="H76" s="20" t="n"/>
       <c r="I76" s="20" t="n"/>
     </row>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
@@ -2089,15 +2052,6 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A80:I80"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>